--- a/2_10_2025_sya_telemeeting (1).xlsx
+++ b/2_10_2025_sya_telemeeting (1).xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9216" windowHeight="4128"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9210" windowHeight="4125"/>
   </bookViews>
   <sheets>
     <sheet name="10tele" sheetId="4" r:id="rId1"/>
@@ -19,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="105">
   <si>
     <t>週間報告について説明させて致します。 </t>
   </si>
@@ -51,9 +46,6 @@
     <t>Konshū kyūka o totta menbā wa orimasen.</t>
   </si>
   <si>
-    <t>Konshū myanmā ni shukujitsu wa gozaimasen.</t>
-  </si>
-  <si>
     <t>shuji hokoku ni tsuite setsumei sa se te ita da kimasu.</t>
   </si>
   <si>
@@ -180,9 +172,6 @@
       </rPr>
       <t>desu.</t>
     </r>
-  </si>
-  <si>
-    <t>山本 (Yamamoto sama kara no)</t>
   </si>
   <si>
     <t>【開発依頼】作業の自動化_UATヘルスチェック</t>
@@ -221,9 +210,6 @@
     <t xml:space="preserve">Raishu ni Tantaitesuto  wo keizoku shi masu. </t>
   </si>
   <si>
-    <t>Kiken wa shigatsu nanoka desu..(4/7/2026)</t>
-  </si>
-  <si>
     <t>【開発依頼】4631_PBxxxxxxxx_(90)バッチ機DISC使用率軽減対応</t>
   </si>
   <si>
@@ -296,9 +282,6 @@
   </si>
   <si>
     <t>Tantaitesuto wa Mi chakushu desu.</t>
-  </si>
-  <si>
-    <t>Kiken wa shigatsu mika desu..(4/3/2026)</t>
   </si>
   <si>
     <t>【定型】信用取引金利優遇条件設定依頼</t>
@@ -481,21 +464,6 @@
     <t>ketsugō tesuto</t>
   </si>
   <si>
-    <t xml:space="preserve">ketsugō tesuto -Shinkō-chū </t>
-  </si>
-  <si>
-    <t>appudeito-yō shiryō: Kanryō</t>
-  </si>
-  <si>
-    <t>Poptree chekku: Mi chakushu</t>
-  </si>
-  <si>
-    <t>Chōsa: Kanryō</t>
-  </si>
-  <si>
-    <t>kaihatsu: Kanryō</t>
-  </si>
-  <si>
     <r>
       <t>Raishu ni Ketsugō tesuto</t>
     </r>
@@ -510,9 +478,6 @@
       </rPr>
       <t xml:space="preserve"> wo keizoku shi masu. </t>
     </r>
-  </si>
-  <si>
-    <t>demo gamen no shūsei: Mi chakushu</t>
   </si>
   <si>
     <t>【定型】株式委託手数料プランの名前変更</t>
@@ -554,9 +519,6 @@
     <t xml:space="preserve">Raishu ni Chōsa PR・WOLFDB wo keizoku shi masu. </t>
   </si>
   <si>
-    <t>Kiken wa shigatsu mika desu..(2026/4/xx)</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -639,13 +601,213 @@
       </rPr>
       <t xml:space="preserve"> wa nihon gawa no shukujitsu desu.(2026/04/29)</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chōsa </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kaihatsu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">wa </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kanryō desu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ketsugō tesuto </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Shinkō-chū desu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">appudeito-yō shiryō </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Kanryō desu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Poptree chekku </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> demo gamen no shūsei </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mi chakushu desu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Konshū </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">no </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sangatsu nijuushichi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nichi (kin'yōbi) wa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> myanmā no shukujitsu desu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Raishū kyūkayotei wa gozaimasen.</t>
+  </si>
+  <si>
+    <t>Raishū shukujitsu wa gozaimasen.</t>
+  </si>
+  <si>
+    <t>Kigen wa shigatsu nanoka desu..(4/7/2026)</t>
+  </si>
+  <si>
+    <t>Kigen wa shigatsu mika desu..(4/3/2026)</t>
+  </si>
+  <si>
+    <t>Kigen wa shigatsu-matsu desu..(2026/4/xx)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -747,6 +909,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -775,7 +942,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -816,6 +983,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -882,7 +1050,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -917,7 +1085,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1127,20 +1295,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:L123"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N124"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.44140625" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" customWidth="1"/>
-    <col min="7" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" customWidth="1"/>
+    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1152,9 +1320,9 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -1164,7 +1332,7 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -1174,7 +1342,7 @@
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -1188,10 +1356,10 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -1200,10 +1368,10 @@
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
       <c r="B6" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1212,10 +1380,10 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -1224,10 +1392,10 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
@@ -1236,7 +1404,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
       <c r="B9" s="3" t="s">
         <v>7</v>
@@ -1248,10 +1416,10 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -1260,7 +1428,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="4"/>
       <c r="C11" s="10"/>
@@ -1270,7 +1438,7 @@
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
         <v>2</v>
       </c>
@@ -1284,38 +1452,38 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="15"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1323,34 +1491,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B23" s="16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B24" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B25" s="16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -1358,535 +1526,540 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
     </row>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B35" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" s="8"/>
+    </row>
+    <row r="41" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B41" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B31" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B32" s="16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B33" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B34" s="16" t="s">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B36" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>4</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="46" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B47" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="L47" s="1"/>
+    </row>
+    <row r="49" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B39" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B40" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F41" s="8"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B42" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B47" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B48" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="L48" s="1"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>5</v>
-      </c>
-      <c r="B50" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B51" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
+    <row r="53" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B53" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B54" s="7" t="s">
+    <row r="59" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B59" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B60" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B61" s="16"/>
+    </row>
+    <row r="62" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="A62">
         <v>6</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B55" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B56" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B57" t="s">
+      <c r="B62" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B63" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="15"/>
+      <c r="D63" s="15"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B58" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B59" t="s">
+    <row r="66" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B66" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B60" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B61" s="4" t="s">
+      <c r="E67" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B62" s="16"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>6</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B64" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B65" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B66" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B67" s="7" t="s">
+      <c r="E68" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B68" t="s">
-        <v>58</v>
-      </c>
-      <c r="E68" s="16" t="s">
+      <c r="E70" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B69" t="s">
-        <v>59</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B70" t="s">
-        <v>28</v>
-      </c>
-      <c r="E70" s="16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B71" t="s">
+      <c r="E71" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E71" s="16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>65</v>
       </c>
-      <c r="E72" s="16" t="s">
+      <c r="E72" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B73" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B74" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B75" s="4"/>
+    </row>
+    <row r="76" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>7</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B77" s="15" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
+      <c r="C77" s="15"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
         <v>69</v>
       </c>
-      <c r="E73" t="s">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B74" s="3" t="s">
+    <row r="80" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B80" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B81" s="4"/>
+    </row>
+    <row r="82" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>8</v>
+      </c>
+      <c r="B82" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B83" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="15"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B75" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B76" s="4"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>7</v>
-      </c>
-      <c r="B77" s="16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B78" s="15" t="s">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
         <v>72</v>
       </c>
-      <c r="C78" s="15"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B79" t="s">
+    </row>
+    <row r="86" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+      <c r="B86" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B80" t="s">
+      <c r="D87" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B81" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B82" s="4"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>75</v>
+      </c>
+      <c r="D89" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>76</v>
+      </c>
+      <c r="D90" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>77</v>
+      </c>
+      <c r="D91" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B93" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B94" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>9</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B97" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="15"/>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B98" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B100" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>89</v>
+      </c>
+      <c r="D101" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>86</v>
+      </c>
+      <c r="D102" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>83</v>
+      </c>
+      <c r="D103" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>84</v>
+      </c>
+      <c r="D104" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>77</v>
+      </c>
+      <c r="D105" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>85</v>
+      </c>
+      <c r="D106" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B107" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B108" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B109" s="16"/>
+    </row>
+    <row r="110" spans="1:14" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B111" s="16"/>
+      <c r="N111" s="16"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B112" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B83" s="16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B84" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="15"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B85" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B86" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B87" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B88" t="s">
-        <v>77</v>
-      </c>
-      <c r="D88" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B89" t="s">
-        <v>78</v>
-      </c>
-      <c r="D89" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B90" t="s">
-        <v>79</v>
-      </c>
-      <c r="D90" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B91" t="s">
-        <v>80</v>
-      </c>
-      <c r="D91" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B92" t="s">
-        <v>81</v>
-      </c>
-      <c r="D92" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B93" t="s">
-        <v>82</v>
-      </c>
-      <c r="D93" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B94" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B95" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97">
+      <c r="F112" s="5"/>
+      <c r="N112" s="18"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
         <v>9</v>
       </c>
-      <c r="B97" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B98" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C98" s="15"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B99" s="16" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B100" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B101" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B102" t="s">
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
         <v>99</v>
       </c>
-      <c r="D102" t="s">
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B115" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B116" s="18" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B103" t="s">
-        <v>96</v>
-      </c>
-      <c r="D103" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B104" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F117" s="5"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B119" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
         <v>93</v>
       </c>
-      <c r="D104" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B105" t="s">
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
         <v>94</v>
       </c>
-      <c r="D105" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B106" t="s">
-        <v>81</v>
-      </c>
-      <c r="D106" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B107" t="s">
-        <v>95</v>
-      </c>
-      <c r="D107" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B108" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B109" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B110" s="16"/>
-    </row>
-    <row r="111" spans="1:4" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.3"/>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B112" s="16"/>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B113" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B114" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B115" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B118" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B119" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B120" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B122" s="5" t="s">
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B123" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B124" s="5" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B123" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/2_10_2025_sya_telemeeting (1).xlsx
+++ b/2_10_2025_sya_telemeeting (1).xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Suan Yee Aung\GIT\t_ok\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EB760F-C90C-4668-8729-A32C5255A120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9210" windowHeight="4125"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10tele" sheetId="4" r:id="rId1"/>
@@ -116,7 +122,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="8" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -126,7 +132,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -141,7 +147,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -156,7 +162,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -166,7 +172,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -229,7 +235,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -239,7 +245,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -254,7 +260,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -263,7 +269,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -273,7 +279,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -312,7 +318,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -322,7 +328,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -349,7 +355,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -359,7 +365,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -377,7 +383,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -387,7 +393,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -403,7 +409,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -414,7 +420,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -472,7 +478,7 @@
         <b/>
         <sz val="11"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -523,7 +529,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF00FF"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -533,7 +539,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -543,7 +549,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -553,7 +559,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF00FF"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -563,7 +569,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -573,7 +579,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -585,7 +591,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF00FF"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -595,7 +601,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -610,7 +616,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -620,7 +626,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -630,7 +636,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -640,7 +646,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -655,7 +661,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -665,7 +671,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -680,7 +686,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -690,7 +696,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -705,7 +711,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -715,7 +721,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -725,7 +731,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -735,7 +741,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -750,7 +756,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -760,7 +766,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -770,7 +776,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -780,7 +786,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -806,12 +812,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="15" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -819,7 +825,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -827,21 +833,21 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -849,14 +855,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF00FF"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -864,27 +870,27 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF00FF"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -897,7 +903,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -905,7 +911,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -913,6 +919,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1008,9 +1021,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1048,7 +1061,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1120,7 +1133,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1293,22 +1306,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:N124"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" customWidth="1"/>
+    <col min="3" max="3" width="18.25" customWidth="1"/>
+    <col min="4" max="4" width="26.375" customWidth="1"/>
+    <col min="5" max="5" width="10.875" customWidth="1"/>
+    <col min="6" max="6" width="24.875" customWidth="1"/>
+    <col min="7" max="8" width="9.75" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1320,7 +1333,7 @@
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:8" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
@@ -1332,7 +1345,7 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
-    <row r="3" spans="1:8" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="11"/>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
@@ -1342,7 +1355,7 @@
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -1356,7 +1369,7 @@
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A5" s="11"/>
       <c r="B5" s="14" t="s">
         <v>18</v>
@@ -1368,7 +1381,7 @@
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
     </row>
-    <row r="6" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" s="11"/>
       <c r="B6" s="11" t="s">
         <v>19</v>
@@ -1380,7 +1393,7 @@
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
     </row>
-    <row r="7" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A7" s="11"/>
       <c r="B7" s="11" t="s">
         <v>20</v>
@@ -1392,7 +1405,7 @@
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" s="11"/>
       <c r="B8" s="11" t="s">
         <v>22</v>
@@ -1404,7 +1417,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
     </row>
-    <row r="9" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A9" s="11"/>
       <c r="B9" s="3" t="s">
         <v>7</v>
@@ -1416,7 +1429,7 @@
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
     </row>
-    <row r="10" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A10" s="11"/>
       <c r="B10" s="4" t="s">
         <v>23</v>
@@ -1428,7 +1441,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" s="11"/>
       <c r="B11" s="4"/>
       <c r="C11" s="10"/>
@@ -1438,7 +1451,7 @@
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" spans="1:8" ht="14.45" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.15">
       <c r="A12" s="12">
         <v>2</v>
       </c>
@@ -1452,38 +1465,38 @@
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B13" s="14" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="15"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B15" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B16" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B17" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1491,34 +1504,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B21" s="14" t="s">
         <v>47</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B22" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B23" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B24" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B25" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>3</v>
       </c>
@@ -1526,49 +1539,49 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="15" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
     </row>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B30" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B31" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B32" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B33" s="16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B35" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>4</v>
       </c>
@@ -1576,55 +1589,55 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B38" s="15" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B39" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>31</v>
       </c>
       <c r="F40" s="8"/>
     </row>
-    <row r="41" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B41" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B42" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B44" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B45" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B46" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B47" s="4" t="s">
         <v>102</v>
       </c>
@@ -1632,7 +1645,7 @@
       <c r="D47" s="2"/>
       <c r="L47" s="1"/>
     </row>
-    <row r="49" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>5</v>
       </c>
@@ -1640,67 +1653,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B50" s="15" t="s">
         <v>47</v>
       </c>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B51" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B52" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B53" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B54" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B55" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B56" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B57" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B58" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B59" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B60" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B61" s="16"/>
     </row>
-    <row r="62" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62">
         <v>6</v>
       </c>
@@ -1708,29 +1721,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B63" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="15"/>
       <c r="D63" s="15"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B64" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B65" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B66" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B67" t="s">
         <v>54</v>
       </c>
@@ -1738,7 +1751,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B68" t="s">
         <v>55</v>
       </c>
@@ -1746,7 +1759,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B69" t="s">
         <v>27</v>
       </c>
@@ -1754,7 +1767,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B70" t="s">
         <v>60</v>
       </c>
@@ -1762,7 +1775,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B71" t="s">
         <v>61</v>
       </c>
@@ -1770,7 +1783,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B72" t="s">
         <v>65</v>
       </c>
@@ -1778,20 +1791,20 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B73" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B74" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B75" s="4"/>
     </row>
-    <row r="76" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76">
         <v>7</v>
       </c>
@@ -1799,31 +1812,31 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B77" s="15" t="s">
         <v>68</v>
       </c>
       <c r="C77" s="15"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B78" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B79" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
       <c r="B80" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B81" s="4"/>
     </row>
-    <row r="82" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82">
         <v>8</v>
       </c>
@@ -1831,28 +1844,28 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B83" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C83" s="15"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B84" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B85" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B86" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B87" t="s">
         <v>73</v>
       </c>
@@ -1860,12 +1873,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B88" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B89" t="s">
         <v>75</v>
       </c>
@@ -1873,7 +1886,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B90" t="s">
         <v>76</v>
       </c>
@@ -1881,7 +1894,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B91" t="s">
         <v>77</v>
       </c>
@@ -1889,22 +1902,22 @@
         <v>98</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B92" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B93" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B94" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96">
         <v>9</v>
       </c>
@@ -1912,28 +1925,28 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B97" s="15" t="s">
         <v>16</v>
       </c>
       <c r="C97" s="15"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B98" s="16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B99" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B100" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B101" t="s">
         <v>89</v>
       </c>
@@ -1941,7 +1954,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B102" t="s">
         <v>86</v>
       </c>
@@ -1949,7 +1962,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B103" t="s">
         <v>83</v>
       </c>
@@ -1957,7 +1970,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B104" t="s">
         <v>84</v>
       </c>
@@ -1965,7 +1978,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B105" t="s">
         <v>77</v>
       </c>
@@ -1973,7 +1986,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B106" t="s">
         <v>85</v>
       </c>
@@ -1981,88 +1994,89 @@
         <v>90</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B107" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B108" s="4" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B109" s="16"/>
     </row>
-    <row r="110" spans="1:14" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.15"/>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A111" s="15" t="s">
         <v>5</v>
       </c>
       <c r="B111" s="16"/>
       <c r="N111" s="16"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B112" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F112" s="5"/>
       <c r="N112" s="18"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B115" s="16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B116" s="18" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
       <c r="F117" s="5"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A118" s="15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B120" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B121" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B123" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B124" s="5" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/2_10_2025_sya_telemeeting (1).xlsx
+++ b/2_10_2025_sya_telemeeting (1).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="104">
   <si>
     <t>週間報告について説明させて致します。 </t>
   </si>
@@ -336,35 +336,7 @@
     <t>UPDATE用資料：進行中</t>
   </si>
   <si>
-    <t>Ketsugō tesuto</t>
-  </si>
-  <si>
     <t>appudeito-yō shiryō</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">appudeito-yō shiryō </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>wa</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  Shinkō-chū desu.</t>
-    </r>
   </si>
   <si>
     <t>Poptreeチェック：未着手</t>
@@ -510,12 +482,6 @@
     <t>調査（PR・WOLFDB）：進行中</t>
   </si>
   <si>
-    <t>demo gamen no shūsei:    - Mi chakushu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chōsa PR・WOLFDB  -- Shinkō-chū </t>
-  </si>
-  <si>
     <t xml:space="preserve">Raishu ni Chōsa PR・WOLFDB wo keizoku shi masu. </t>
   </si>
   <si>
@@ -801,6 +767,101 @@
   </si>
   <si>
     <t>Kigen wa shigatsu-matsu desu..(2026/4/xx)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chōsa PR・WOLFDB  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Shinkō-chū  desu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">demo gamen no shūsei </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">wa </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mi chakushu desu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ketsugō tesuto </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> appudeito-yō shiryō </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  Shinkō-chū desu.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1626,7 +1687,7 @@
     </row>
     <row r="47" spans="1:12" ht="14.45" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -1657,7 +1718,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B53" s="7" t="s">
         <v>6</v>
       </c>
@@ -1682,25 +1743,25 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B59" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B60" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B61" s="16"/>
     </row>
-    <row r="62" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>6</v>
       </c>
@@ -1725,7 +1786,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B66" s="7" t="s">
         <v>56</v>
       </c>
@@ -1758,40 +1819,38 @@
       <c r="B70" t="s">
         <v>60</v>
       </c>
-      <c r="E70" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="E70" s="16"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>61</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E72" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B73" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B74" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B75" s="4"/>
     </row>
-    <row r="76" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>7</v>
       </c>
@@ -1801,29 +1860,29 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C77" s="15"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="14.45" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B80" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B81" s="4"/>
     </row>
-    <row r="82" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>8</v>
       </c>
@@ -1839,69 +1898,69 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="14.45" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B86" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D87" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D89" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D90" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D91" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B93" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B94" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -1920,12 +1979,12 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B98" s="16" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
@@ -1935,60 +1994,60 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D101" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D102" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D103" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D105" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D106" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B107" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B108" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
@@ -2016,17 +2075,17 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B115" s="16" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B116" s="18" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -2044,12 +2103,12 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
